--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="不合规明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按支付通道" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按门店" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按所属分公司" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="不合规明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="按支付通道" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="按门店" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="按所属分公司" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21,079</t>
+          <t>21,076</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,660</t>
+          <t>19,658</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1,179</t>
+          <t>1,178</t>
         </is>
       </c>
     </row>
@@ -527,108 +527,120 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>剔除笔数（退货订单，不计入）</t>
+          <t>剔除笔数（门店所属分公司标记剔除，不计入）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,775</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>剔除笔数（退货订单，不计入）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1,775</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>规则未覆盖笔数</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>笔数</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>金额(元)</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>合规</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19,660</t>
+          <t>笔数</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>72,866,396.21</t>
+          <t>金额(元)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>不合规</t>
+          <t>合规</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>19,658</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1,157,217.46</t>
+          <t>72,865,681.21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>剔除</t>
+          <t>不合规</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1,179</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7,134,904.83</t>
+          <t>1,157,217.46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>剔除</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1,178</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7,133,530.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>规则未覆盖</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>4,499.0</t>
         </is>
@@ -15331,12 +15343,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,099</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7,068,900.66</t>
+          <t>7,067,526.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15351,7 +15363,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,099</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -15849,17 +15861,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>752,383.0</t>
+          <t>752,067.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -16071,17 +16083,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>90,138.0</t>
+          <t>89,739.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -16777,7 +16789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22313,102 +22325,6 @@
       <c r="F173" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>APR昆明同德广场</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>四川新跃内购店</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>316.0</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>APR昆明七彩云南</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>1,374.19</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -22423,7 +22339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22594,17 +22510,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2,477</t>
+          <t>2,964</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9,947,798.69</t>
+          <t>11,866,078.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2,348</t>
+          <t>2,808</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -22614,7 +22530,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.66%</t>
+          <t>99.72%</t>
         </is>
       </c>
     </row>
@@ -22647,166 +22563,6 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>99.83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>（旧）APR成都凯德魅力城</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>579,700.02</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>（旧）APR成都环球中心</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>593,617.72</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>（旧）APR成都天府环宇坊</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>452,489.05</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>（旧）APR成都东安天街</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>292,472.74</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>剔除</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2,089.19</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -22339,7 +22339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22373,6 +22373,21 @@
           <t>分公司合规率</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>合规门店数量</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>不合规门店数量</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>100%合规门店占比</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22405,6 +22420,21 @@
           <t>98.56%</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>27.0%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22437,6 +22467,21 @@
           <t>98.49%</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22469,6 +22514,21 @@
           <t>98.76%</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>51.4%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22501,6 +22561,21 @@
           <t>97.67%</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22533,6 +22608,21 @@
           <t>99.72%</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22563,6 +22653,21 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>99.83%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
         </is>
       </c>
     </row>

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -22350,42 +22350,42 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>合规门店数量</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>不合规门店数量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>100%合规门店占比</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>笔数</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>金额(元)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>合规</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>不合规</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>分公司合规率</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>合规门店数量</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>不合规门店数量</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>100%合规门店占比</t>
         </is>
       </c>
     </row>
@@ -22397,42 +22397,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>27.0%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>6,473</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>24,971,246.54</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>6,010</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>98.56%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>27.0%</t>
         </is>
       </c>
     </row>
@@ -22444,42 +22444,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>5,835</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>24,854,211.39</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>5,351</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>98.49%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -22491,42 +22491,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>51.4%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2,861</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>9,357,404.74</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2,702</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>98.76%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -22538,42 +22538,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>1,059</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>3,245,256.34</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>1,004</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>97.67%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -22585,42 +22585,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2,964</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>11,866,078.22</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2,808</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>99.72%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -22632,42 +22632,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>1,884</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>6,866,731.08</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>1,783</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>99.83%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90.0%</t>
         </is>
       </c>
     </row>

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -419,6 +419,9 @@
   </sheetPr>
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -15075,6 +15078,9 @@
   </sheetPr>
   <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -16791,6 +16797,9 @@
   </sheetPr>
   <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -22341,6 +22350,9 @@
   </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -662,6 +662,9 @@
   </sheetPr>
   <dimension ref="A1:L240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -660,11 +660,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L240"/>
+  <dimension ref="A1:K240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -709,20 +706,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>实收金额</t>
+          <t>会员手机号</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>会员手机号</t>
+          <t>第三方订单号</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>第三方订单号</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -769,20 +761,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>2874</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150****6552</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>150****6552</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -829,20 +818,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>3808</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>177****0229</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>177****0229</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -889,20 +875,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>7781.6</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>158****7998</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>158****7998</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -949,20 +932,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>2297</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>135****5494</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1009,20 +989,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>2397</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>135****5494</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1069,20 +1046,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>3650.52</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>186****9677</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>186****9677</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1129,20 +1103,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>23988</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1189,20 +1160,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>2598</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1249,20 +1217,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1155</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>188****7855</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1309,20 +1274,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1155</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>188****7855</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1369,20 +1331,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1647</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>188****7855</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1429,20 +1388,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>5087</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>137****9080</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>137****9080</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1489,20 +1445,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>24</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1549,20 +1502,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>289</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>138****4526</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>138****4526</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1609,20 +1559,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>199</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>138****5533</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>138****5533</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1669,20 +1616,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>2499</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1729,20 +1673,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>3988</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1789,20 +1730,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>15693</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>185****5918</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>185****5918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1849,20 +1787,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>32084</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>185****5918</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>185****5918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1909,20 +1844,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>4687</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>188****3772</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>188****3772</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -1969,20 +1901,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>4547</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>183****5937</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>183****5937</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2029,20 +1958,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>599</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2089,20 +2015,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>349</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>189****1806</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>189****1806</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2149,20 +2072,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>3799</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>139****1884</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>139****1884</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2209,20 +2129,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>249</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+86-150****9917</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>+86-150****9917</t>
+          <t>2083435200665018369</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
-        <is>
-          <t>2083435200665018369</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2269,20 +2186,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>598</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+86-135****9969</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+86-135****9969</t>
+          <t>2083485389348970505</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
-        <is>
-          <t>2083485389348970505</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2329,20 +2243,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>10198.1</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+86-139****7048</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+86-139****7048</t>
+          <t>2083476392870047750</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
-        <is>
-          <t>2083476392870047750</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2389,20 +2300,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>6499</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+86-155****0158</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+86-155****0158</t>
+          <t>2083434705134288904</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
-        <is>
-          <t>2083434705134288904</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2449,20 +2357,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>11499</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+86-134****7207</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+86-134****7207</t>
+          <t>2083399273130491907</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
-        <is>
-          <t>2083399273130491907</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2509,20 +2414,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>1849</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>2083530245690810368</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
-        <is>
-          <t>2083530245690810368</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2569,20 +2471,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>1298</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>+86-152****2966</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+86-152****2966</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2629,20 +2528,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>1099</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>+86-150****7583</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+86-150****7583</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2689,20 +2585,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>1099</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+86-132****8817</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>+86-132****8817</t>
+          <t>20834194****6625799</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
-        <is>
-          <t>20834194****6625799</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2749,20 +2642,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>11499</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+86-135****9925</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+86-135****9925</t>
+          <t>2083378868570218500</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
-        <is>
-          <t>2083378868570218500</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2809,20 +2699,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>149</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+86-158****6671</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+86-158****6671</t>
+          <t>208345132****212679</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
-        <is>
-          <t>208345132****212679</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2869,20 +2756,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>9797</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+86-185****8868</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>+86-185****8868</t>
+          <t>2083393526554419209</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
-        <is>
-          <t>2083393526554419209</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2929,20 +2813,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>139</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+86-182****9334</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+86-182****9334</t>
+          <t>2083438481639473158</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
-        <is>
-          <t>2083438481639473158</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -2989,20 +2870,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>9097</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+86-137****3437</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+86-137****3437</t>
+          <t>20835186****4193281</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
-        <is>
-          <t>20835186****4193281</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3049,20 +2927,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>598</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+86-176****6676</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>+86-176****6676</t>
+          <t>2083488925279584260</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
-        <is>
-          <t>2083488925279584260</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3109,20 +2984,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>598</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+86-176****6676</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+86-176****6676</t>
+          <t>2083489110968659969</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
-        <is>
-          <t>2083489110968659969</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3169,20 +3041,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>299</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>157****5096</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>157****5096</t>
+          <t>20835184****5394950</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
-        <is>
-          <t>20835184****5394950</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3229,20 +3098,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>1298</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+86-137****4592</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+86-137****4592</t>
+          <t>2083468249950625799</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
-        <is>
-          <t>2083468249950625799</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3289,20 +3155,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>10597</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+86-137****5157</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>+86-137****5157</t>
+          <t>2083459403900444673</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
-        <is>
-          <t>2083459403900444673</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3349,20 +3212,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>9597</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+86-185****6381</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>+86-185****6381</t>
+          <t>2083492041394888704</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
-        <is>
-          <t>2083492041394888704</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3409,20 +3269,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>149</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+86-189****6101</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>+86-189****6101</t>
+          <t>2083535221353807878</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
-        <is>
-          <t>2083535221353807878</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3469,20 +3326,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>149</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+86-136****1011</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+86-136****1011</t>
+          <t>2083473729850638338</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
-        <is>
-          <t>2083473729850638338</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3529,20 +3383,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>268</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+86-139****5572</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>+86-139****5572</t>
+          <t>2083466044125376518</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
-        <is>
-          <t>2083466044125376518</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3589,20 +3440,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>1298</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+86-138****9496</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>+86-138****9496</t>
+          <t>20834627171****4854</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
-        <is>
-          <t>20834627171****4854</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3649,20 +3497,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>2196</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+86-136****7692</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>+86-136****7692</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3709,20 +3554,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>798</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+86-136****7692</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+86-136****7692</t>
+          <t>2083869093608218625</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
-        <is>
-          <t>2083869093608218625</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3769,20 +3611,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>13096</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+86-139****3343</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>+86-139****3343</t>
+          <t>20838158****0227969</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
-        <is>
-          <t>20838158****0227969</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3829,20 +3668,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1197</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+86-134****3653</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>+86-134****3653</t>
+          <t>2083862067750772743</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
-        <is>
-          <t>2083862067750772743</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3889,20 +3725,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>9997.1</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+86-138****0953</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>+86-138****0953</t>
+          <t>2083867893785956356</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
-        <is>
-          <t>2083867893785956356</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -3949,20 +3782,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>10717.19</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+86-139****1898</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+86-139****1898</t>
+          <t>2083866761469034502</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
-        <is>
-          <t>2083866761469034502</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4009,20 +3839,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>149</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+86-151****6728</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>+86-151****6728</t>
+          <t>2083827033647800321</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
-        <is>
-          <t>2083827033647800321</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4069,20 +3896,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>1099</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+86-153****6593</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>+86-153****6593</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4129,20 +3953,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>10708.96</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+86-133****6806</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>+86-133****6806</t>
+          <t>2083826879054483456</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
-        <is>
-          <t>2083826879054483456</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4189,20 +4010,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>1797</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+86-133****6806</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>+86-133****6806</t>
+          <t>2083829974604701703</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
-        <is>
-          <t>2083829974604701703</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4249,20 +4067,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>12597</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+86-186****0160</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>+86-186****0160</t>
+          <t>2083784830620794886</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
-        <is>
-          <t>2083784830620794886</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4309,20 +4124,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>9499</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>+86-186****3020</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>+86-186****3020</t>
+          <t>2083843530738790407</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
-        <is>
-          <t>2083843530738790407</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4369,20 +4181,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>1499</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>131****2129</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>131****2129</t>
+          <t>2083903589702107144</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
-        <is>
-          <t>2083903589702107144</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4429,20 +4238,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>12598.1</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>131****0218</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>131****0218</t>
+          <t>2083889439111569410</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
-        <is>
-          <t>2083889439111569410</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4489,20 +4295,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>1298</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>+86-135****1432</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>+86-135****1432</t>
+          <t>2083845611390427142</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
-        <is>
-          <t>2083845611390427142</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4549,20 +4352,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>12597</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>+86-150****3779</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>+86-150****3779</t>
+          <t>20838448191****0534</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
-        <is>
-          <t>20838448191****0534</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4609,20 +4409,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>9997.1</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>+86-132****0974</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>+86-132****0974</t>
+          <t>2083842589323927554</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
-        <is>
-          <t>2083842589323927554</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4669,20 +4466,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>1596</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+86-185****8209</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>+86-185****8209</t>
+          <t>2083880794776854530</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
-        <is>
-          <t>2083880794776854530</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4729,20 +4523,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>698</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>137****3613</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>137****3613</t>
+          <t>2083796531577610241</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
-        <is>
-          <t>2083796531577610241</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4789,20 +4580,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>9597</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+86-139****3728</t>
+        </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>+86-139****3728</t>
+          <t>2083746005818204162</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
-        <is>
-          <t>2083746005818204162</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4849,20 +4637,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>11997.1</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>+86-138****9653</t>
+        </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>+86-138****9653</t>
+          <t>2083865579702910982</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
-        <is>
-          <t>2083865579702910982</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4909,20 +4694,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>11499</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+86-185****2293</t>
+        </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>+86-185****2293</t>
+          <t>2083837986196086788</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
-        <is>
-          <t>2083837986196086788</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -4969,20 +4751,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>1298</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+86-185****1539</t>
+        </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>+86-185****1539</t>
+          <t>20838526155****1762</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
-        <is>
-          <t>20838526155****1762</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5029,20 +4808,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>1649</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+86-185****3180</t>
+        </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>+86-185****3180</t>
+          <t>20838160****6694656</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
-        <is>
-          <t>20838160****6694656</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5089,20 +4865,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>2300</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+86-136****7990</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>+86-136****7990</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5149,20 +4922,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>1499</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+86-176****7389</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>+86-176****7389</t>
+          <t>2083805331313393670</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
-        <is>
-          <t>2083805331313393670</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5209,20 +4979,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>9499</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>+86-186****0666</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>+86-186****0666</t>
+          <t>2083776290631974912</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
-        <is>
-          <t>2083776290631974912</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5269,20 +5036,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>399</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>2084201196****13991</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
-        <is>
-          <t>2084201196****13991</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5329,20 +5093,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>399</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>2084147****63665921</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
-        <is>
-          <t>2084147****63665921</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5389,20 +5150,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>699</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>134****0961</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>134****0961</t>
+          <t>208422192****579527</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
-        <is>
-          <t>208422192****579527</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5449,20 +5207,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>999</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>+86-136****7388</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>+86-136****7388</t>
+          <t>2084190****27176713</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
-        <is>
-          <t>2084190****27176713</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5509,20 +5264,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>1298</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>+86-178****3201</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>+86-178****3201</t>
+          <t>2084152****70605063</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
-        <is>
-          <t>2084152****70605063</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5569,20 +5321,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>897</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>+86-137****1675</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>+86-137****1675</t>
+          <t>2084232492481650697</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
-        <is>
-          <t>2084232492481650697</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5629,20 +5378,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>798</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>+86-139****8193</t>
+        </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>+86-139****8193</t>
+          <t>2084157****42969605</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
-        <is>
-          <t>2084157****42969605</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5689,20 +5435,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>399</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>+86-136****0631</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>+86-136****0631</t>
+          <t>2084187****44460808</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
-        <is>
-          <t>2084187****44460808</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5749,20 +5492,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>10597</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>+86-196****1061</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>+86-196****1061</t>
+          <t>2084252509638729731</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
-        <is>
-          <t>2084252509638729731</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5809,20 +5549,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>12597</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>+86-136****5703</t>
+        </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>+86-136****5703</t>
+          <t>2084192****75429636</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
-        <is>
-          <t>2084192****75429636</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5869,20 +5606,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>1499</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>+86-185****5271</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>+86-185****5271</t>
+          <t>2083508592578330630</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
-        <is>
-          <t>2083508592578330630</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5929,20 +5663,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>5999</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>+86-158****2008</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>+86-158****2008</t>
+          <t>2084194****66958086</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
-        <is>
-          <t>2084194****66958086</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -5989,20 +5720,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>598</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>+86-136****9757</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>+86-136****9757</t>
+          <t>2084255436819595267</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
-        <is>
-          <t>2084255436819595267</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6049,20 +5777,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>9299</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>+86-135****0613</t>
+        </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>+86-135****0613</t>
+          <t>2084222032561561600</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
-        <is>
-          <t>2084222032561561600</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6109,20 +5834,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>2598</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>+86-135****0861</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>+86-135****0861</t>
+          <t>2084178****98749443</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
-        <is>
-          <t>2084178****98749443</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6169,20 +5891,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>10299</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>+86-158****3837</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>+86-158****3837</t>
+          <t>2084480634701414408</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
-        <is>
-          <t>2084480634701414408</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6229,20 +5948,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>11597</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>139****2395</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>139****2395</t>
+          <t>2084584776910643202</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
-        <is>
-          <t>2084584776910643202</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6289,20 +6005,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>1399</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>+86-187****2618</t>
+        </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>+86-187****2618</t>
+          <t>2084577203302047747</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
-        <is>
-          <t>2084577203302047747</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6349,20 +6062,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>9597</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>131****3818</t>
+        </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>131****3818</t>
+          <t>2084582420416565255</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
-        <is>
-          <t>2084582420416565255</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6409,20 +6119,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>12597</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>+86-139****8525</t>
+        </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>+86-139****8525</t>
+          <t>2084563295659663364</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
-        <is>
-          <t>2084563295659663364</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6469,20 +6176,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>12597</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>+86-182****5723</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>+86-182****5723</t>
+          <t>2084556561731788801</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
-        <is>
-          <t>2084556561731788801</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6529,20 +6233,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>10717.19</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>+86-159****1014</t>
+        </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>+86-159****1014</t>
+          <t>2084578829391523842</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
-        <is>
-          <t>2084578829391523842</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6589,20 +6290,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>798</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>166****7206</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>166****7206</t>
+          <t>208491136****602752</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
-        <is>
-          <t>208491136****602752</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6649,20 +6347,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>21598</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>181****9239</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>181****9239</t>
+          <t>2084600368103059462</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
-        <is>
-          <t>2084600368103059462</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6709,20 +6404,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>1298</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>+86-133****2199</t>
+        </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>+86-133****2199</t>
+          <t>20849153****8691337</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
-        <is>
-          <t>20849153****8691337</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6769,20 +6461,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>368</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>+86-184****8888</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>+86-184****8888</t>
+          <t>20849152****7220613</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
-        <is>
-          <t>20849152****7220613</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6829,20 +6518,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>1378</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>+86-186****4657</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>+86-186****4657</t>
+          <t>2084894536964186120</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
-        <is>
-          <t>2084894536964186120</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6889,20 +6575,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>11299</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>+86-137****9681</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>+86-137****9681</t>
+          <t>2084829482505408520</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
-        <is>
-          <t>2084829482505408520</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -6949,20 +6632,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>798</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>135****4525</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>135****4525</t>
+          <t>2084871296859967489</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
-        <is>
-          <t>2084871296859967489</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7009,20 +6689,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>1399</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>139****8322</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>139****8322</t>
+          <t>20849195****6447749</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
-        <is>
-          <t>20849195****6447749</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7069,20 +6746,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>10097</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>+86-183****7567</t>
+        </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>+86-183****7567</t>
+          <t>2084924210010554374</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
-        <is>
-          <t>2084924210010554374</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7129,20 +6803,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>12595</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>+86-137****7668</t>
+        </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>+86-137****7668</t>
+          <t>20849165****9137415</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
-        <is>
-          <t>20849165****9137415</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7189,20 +6860,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>9299</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>+86-187****2384</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>+86-187****2384</t>
+          <t>2084998687974752260</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
-        <is>
-          <t>2084998687974752260</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7249,20 +6917,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>498</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>+86-182****6555</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>+86-182****6555</t>
+          <t>2084975273100976130</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
-        <is>
-          <t>2084975273100976130</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7309,20 +6974,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>298</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>+86-139****1165</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>+86-139****1165</t>
+          <t>2084974748826144775</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
-        <is>
-          <t>2084974748826144775</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7369,20 +7031,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>649</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>+86-151****4504</t>
+        </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>+86-151****4504</t>
+          <t>2084883374583341065</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
-        <is>
-          <t>2084883374583341065</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7429,20 +7088,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>498</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>+86-150****7892</t>
+        </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>+86-150****7892</t>
+          <t>2084852832236150789</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
-        <is>
-          <t>2084852832236150789</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7489,20 +7145,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>66</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>+86-139****2518</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>+86-139****2518</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7549,20 +7202,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>14500</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>+86-186****1534</t>
+        </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>+86-186****1534</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7609,20 +7259,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>13799</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>+86-158****6261</t>
+        </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>+86-158****6261</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7669,20 +7316,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>199</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>+86-186****9666</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>+86-186****9666</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7729,20 +7373,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>100</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>+86-138****2964</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>+86-138****2964</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7789,20 +7430,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>200</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>+86-137****5245</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>+86-137****5245</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7849,20 +7487,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>11999</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>+86-133****6607</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>+86-133****6607</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -7909,20 +7544,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>4479</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>+86-158****9578</t>
+        </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>+86-158****9578</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -7969,20 +7601,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>199</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8029,20 +7658,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>10499</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>+86-190****1802</t>
+        </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>+86-190****1802</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8089,20 +7715,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>19999</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>+86-156****1888</t>
+        </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>+86-156****1888</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8149,20 +7772,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>579</v>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>+86-136****0769</t>
+        </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>+86-136****0769</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8209,20 +7829,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>15496</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8269,20 +7886,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>12999</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8329,20 +7943,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>11499</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>+86-186****7992</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>+86-186****7992</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8389,20 +8000,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>8508</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>135****5178</t>
+        </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>135****5178</t>
+          <t>260801000210361243</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
-        <is>
-          <t>260801000210361243</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -8449,20 +8057,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>8508</v>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>135****5178</t>
+        </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>135****5178</t>
+          <t>260801000210359210</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
-        <is>
-          <t>260801000210359210</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -8509,20 +8114,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>7499</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>158****6735</t>
+        </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>158****6735</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8569,20 +8171,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>3</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>185****8918</t>
+        </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>185****8918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8629,20 +8228,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>11500</v>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>185****8918</t>
+        </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>185****8918</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8689,20 +8285,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>100</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>+86-139****8563</t>
+        </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>+86-139****8563</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8749,20 +8342,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>1199</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>+86-186****3681</t>
+        </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>+86-186****3681</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8809,20 +8399,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>11999</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>+86-132****5290</t>
+        </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>+86-132****5290</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8869,20 +8456,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>14999</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>+86-189****0781</t>
+        </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>+86-189****0781</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8929,20 +8513,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>12999</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>+86-137****4764</t>
+        </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>+86-137****4764</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -8989,20 +8570,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>1319</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>+86-173****8086</t>
+        </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>+86-173****8086</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9049,20 +8627,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>200</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>+86-133****8655</t>
+        </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>+86-133****8655</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9109,20 +8684,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>200</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>+86-133****3358</t>
+        </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>+86-133****3358</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -9169,20 +8741,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>199</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>+86-137****3871</t>
+        </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>+86-137****3871</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9229,20 +8798,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>1199</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>+86-135****2380</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>+86-135****2380</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9289,20 +8855,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>69</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>+86-187****1204</t>
+        </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>+86-187****1204</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9349,20 +8912,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>13999</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>+86-158****7802</t>
+        </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>+86-158****7802</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9409,20 +8969,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>1249</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>+86-137****5188</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>+86-137****5188</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9469,20 +9026,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>4498</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>+86-156****9614</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>+86-156****9614</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9529,20 +9083,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>9196</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9589,20 +9140,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>6999</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9649,20 +9197,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>16497</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9709,20 +9254,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>12699</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>+86-139****3939</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>+86-139****3939</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9769,20 +9311,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>12500</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>+86-132****9058</t>
+        </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>+86-132****9058</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9829,20 +9368,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>300</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>+86-185****8357</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>+86-185****8357</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9889,20 +9425,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>50</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>+86-151****4775</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>+86-151****4775</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -9949,20 +9482,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>599</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10009,20 +9539,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>599</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -10069,20 +9596,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>12599</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10129,20 +9653,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>199</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>+86-131****8359</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>+86-131****8359</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -10189,20 +9710,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>49</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>139****9854</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>139****9854</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10249,20 +9767,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>8299</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>+86-158****7802</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>+86-158****7802</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10309,20 +9824,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>13800</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>+86-188****0892</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>+86-188****0892</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10369,20 +9881,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>10</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>+86-136****3866</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>+86-136****3866</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10429,20 +9938,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>5197</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>+86-186****2999</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>+86-186****2999</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10489,20 +9995,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>99</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>+86-136****4596</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>+86-136****4596</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10549,20 +10052,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>200</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>+86-135****3541</t>
+        </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>+86-135****3541</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10609,20 +10109,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>85</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>+86-136****6230</t>
+        </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>+86-136****6230</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10669,20 +10166,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>1000</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>+86-135****7391</t>
+        </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>+86-135****7391</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10729,20 +10223,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>6899</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>+86-187****9725</t>
+        </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>+86-187****9725</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10789,20 +10280,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>99</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>+86-136****2871</t>
+        </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>+86-136****2871</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10849,20 +10337,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>99</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>+86-136****4417</t>
+        </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>+86-136****4417</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -10909,20 +10394,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>299</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>+86-139****6913</t>
+        </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>+86-139****6913</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -10969,20 +10451,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>100</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>+86-136****5348</t>
+        </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>+86-136****5348</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11029,20 +10508,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>1149</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>+86-135****7766</t>
+        </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>+86-135****7766</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11089,20 +10565,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>1</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>+86-178****1967</t>
+        </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>+86-178****1967</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11149,20 +10622,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>0.1</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>153****1994</t>
+        </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>153****1994</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11209,20 +10679,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>3799</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>+86-156****9614</t>
+        </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>+86-156****9614</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11269,20 +10736,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>4597</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>+86-151****0897</t>
+        </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>+86-151****0897</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11329,20 +10793,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>200</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>+86-185****1770</t>
+        </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>+86-185****1770</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11389,20 +10850,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>10299</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>+86-187****8972</t>
+        </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>+86-187****8972</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11449,20 +10907,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>498</v>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>+86-158****1870</t>
+        </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>+86-158****1870</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11509,20 +10964,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>194</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>188****2372</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>188****2372</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11569,20 +11021,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>500</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>133****0100</t>
+        </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>133****0100</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11629,20 +11078,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>0.4</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>133****0100</t>
+        </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>133****0100</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11689,20 +11135,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>200</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>+86-198****6299</t>
+        </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>+86-198****6299</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11749,20 +11192,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>500</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>+86-198****6299</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>+86-198****6299</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11809,20 +11249,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>22497</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>+86-152****5172</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>+86-152****5172</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11869,20 +11306,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>19299</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>+86-152****5512</t>
+        </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>+86-152****5512</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -11929,20 +11363,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>4201</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>+86-176****1972</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>+86-176****1972</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -11989,20 +11420,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>1899</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>189****0307</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>189****0307</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12049,20 +11477,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>8299</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>182****4561</t>
+        </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>182****4561</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12109,20 +11534,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>778</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>+86-185****1711</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>+86-185****1711</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12169,20 +11591,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>12799</v>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>+86-133****4816</t>
+        </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>+86-133****4816</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12229,20 +11648,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>11699</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>+86-132****0312</t>
+        </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>+86-132****0312</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12289,20 +11705,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>7299</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>139****5407</t>
+        </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>139****5407</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12349,20 +11762,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>1999</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>+86-186****2128</t>
+        </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>+86-186****2128</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -12409,20 +11819,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>2999</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12469,20 +11876,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>4026</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12529,20 +11933,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>599</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12589,20 +11990,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>3917</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>177****2965</t>
+        </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>177****2965</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12649,20 +12047,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>1398</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>184****5224</t>
+        </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>184****5224</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12709,20 +12104,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>3697</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12769,20 +12161,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I202" t="n">
-        <v>5999</v>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12829,20 +12218,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I203" t="n">
-        <v>2767</v>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>137****2423</t>
+        </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>137****2423</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12889,20 +12275,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I204" t="n">
-        <v>3799</v>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -12949,20 +12332,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I205" t="n">
-        <v>3218</v>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13009,20 +12389,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I206" t="n">
-        <v>3355</v>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>135****5980</t>
+        </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13069,20 +12446,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I207" t="n">
-        <v>2298</v>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>135****5980</t>
+        </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13129,20 +12503,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I208" t="n">
-        <v>5499</v>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>158****9456</t>
+        </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>158****9456</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13189,20 +12560,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I209" t="n">
-        <v>558</v>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>+86-183****7721</t>
+        </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>+86-183****7721</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13249,20 +12617,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I210" t="n">
-        <v>1698</v>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13309,20 +12674,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I211" t="n">
-        <v>4174</v>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13369,20 +12731,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I212" t="n">
-        <v>3799</v>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13429,20 +12788,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I213" t="n">
-        <v>3799</v>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13489,20 +12845,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I214" t="n">
-        <v>3898</v>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>172****4364</t>
+        </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>172****4364</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13549,20 +12902,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I215" t="n">
-        <v>5244</v>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>138****7017</t>
+        </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>138****7017</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13609,20 +12959,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I216" t="n">
-        <v>5845</v>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>135****5980</t>
+        </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13669,20 +13016,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I217" t="n">
-        <v>699</v>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13729,20 +13073,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I218" t="n">
-        <v>4299</v>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>138****1500</t>
+        </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>138****1500</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13789,20 +13130,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I219" t="n">
-        <v>3108</v>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>157****2651</t>
+        </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>157****2651</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13849,20 +13187,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I220" t="n">
-        <v>3799</v>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>134****2963</t>
+        </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>134****2963</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13909,20 +13244,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I221" t="n">
-        <v>23655</v>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>186****1441</t>
+        </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>186****1441</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -13969,20 +13301,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I222" t="n">
-        <v>3799</v>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>186****9390</t>
+        </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>186****9390</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14029,20 +13358,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I223" t="n">
-        <v>4334</v>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>152****3830</t>
+        </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>152****3830</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14089,20 +13415,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I224" t="n">
-        <v>1299</v>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14149,20 +13472,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I225" t="n">
-        <v>3646</v>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>173****2982</t>
+        </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>173****2982</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14209,20 +13529,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I226" t="n">
-        <v>5999</v>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>135****2633</t>
+        </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>135****2633</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14269,20 +13586,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I227" t="n">
-        <v>4148</v>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>151****7380</t>
+        </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>151****7380</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14329,20 +13643,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I228" t="n">
-        <v>159</v>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>134****3737</t>
+        </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>134****3737</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14389,20 +13700,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I229" t="n">
-        <v>3827</v>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14449,20 +13757,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I230" t="n">
-        <v>198</v>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>+86-181****3714</t>
+        </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>+86-181****3714</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14509,20 +13814,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I231" t="n">
-        <v>280</v>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>+86-134****6425</t>
+        </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>+86-134****6425</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14569,20 +13871,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I232" t="n">
-        <v>198</v>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>+86-186****1921</t>
+        </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>+86-186****1921</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14629,20 +13928,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I233" t="n">
-        <v>100</v>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>+86-159****4633</t>
+        </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>+86-159****4633</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14689,20 +13985,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I234" t="n">
-        <v>2699</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>+86-136****8289</t>
+        </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>+86-136****8289</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14749,20 +14042,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I235" t="n">
-        <v>178</v>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>139****7878</t>
+        </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>139****7878</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14809,20 +14099,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I236" t="n">
-        <v>178</v>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>139****0299</t>
+        </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>139****0299</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14869,20 +14156,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I237" t="n">
-        <v>280</v>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>159****9395</t>
+        </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>159****9395</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr">
         <is>
           <t>不合规（缺三方单号）</t>
         </is>
@@ -14929,20 +14213,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I238" t="n">
-        <v>79</v>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>+86-178****0594</t>
+        </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>+86-178****0594</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -14989,20 +14270,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I239" t="n">
-        <v>7499</v>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>+86-189****0178</t>
+        </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>+86-189****0178</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>
@@ -15049,20 +14327,17 @@
           <t>销售收款</t>
         </is>
       </c>
-      <c r="I240" t="n">
-        <v>799</v>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>+86-130****1120</t>
+        </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>+86-130****1120</t>
+          <t>（无）</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
-        <is>
-          <t>（无）</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr">
         <is>
           <t>不合规（公司禁用收款通道）</t>
         </is>

--- a/cashier/收银合规分析.xlsx
+++ b/cashier/收银合规分析.xlsx
@@ -417,11 +417,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -575,11 +572,6 @@
           <t>笔数</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>金额(元)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -592,11 +584,6 @@
           <t>19,658</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>72,865,681.21</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -609,11 +596,6 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1,157,217.46</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -626,11 +608,6 @@
           <t>1,178</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7,133,530.64</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -641,11 +618,6 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4,499.0</t>
         </is>
       </c>
     </row>
@@ -14354,11 +14326,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -14373,25 +14342,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>金额(元)</t>
+          <t>合规</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>合规</t>
+          <t>不合规</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>不合规</t>
+          <t>剔除</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>剔除</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>规则未覆盖</t>
         </is>
@@ -14410,12 +14374,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13,138,238.35</t>
+          <t>3,339</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3,339</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14424,11 +14388,6 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14447,12 +14406,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13,136,002.35</t>
+          <t>3,338</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3,338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14461,11 +14420,6 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14484,12 +14438,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9,118,510.62</t>
+          <t>3,053</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3,053</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -14498,11 +14452,6 @@
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14521,12 +14470,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7,417,755.95</t>
+          <t>1,971</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1,971</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14535,11 +14484,6 @@
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14558,12 +14502,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5,102,673.65</t>
+          <t>1,322</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1,322</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -14572,11 +14516,6 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14595,12 +14534,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3,708,168.48</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -14609,11 +14548,6 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14632,7 +14566,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7,067,526.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14642,15 +14576,10 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,099</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>1,099</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14669,25 +14598,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5,506,970.92</t>
+          <t>881</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14706,12 +14630,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2,448,239.9</t>
+          <t>877</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -14720,11 +14644,6 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14743,12 +14662,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1,402,618.84</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -14757,11 +14676,6 @@
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14780,12 +14694,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1,897,208.0</t>
+          <t>545</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -14794,11 +14708,6 @@
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14817,12 +14726,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1,552,600.85</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14831,11 +14740,6 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14854,12 +14758,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1,198,852.55</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -14868,11 +14772,6 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14891,12 +14790,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>974,988.96</t>
+          <t>342</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -14905,11 +14804,6 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14928,12 +14822,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>999,808.8</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -14942,11 +14836,6 @@
         </is>
       </c>
       <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -14965,12 +14854,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1,178,693.1</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -14979,11 +14868,6 @@
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15002,12 +14886,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>189,766.05</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -15016,11 +14900,6 @@
         </is>
       </c>
       <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15039,25 +14918,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>759,452.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15076,12 +14950,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>422,759.0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -15090,11 +14964,6 @@
         </is>
       </c>
       <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15113,12 +14982,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>946,326.4</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -15127,11 +14996,6 @@
         </is>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15150,12 +15014,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>752,067.0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -15164,11 +15028,6 @@
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15187,7 +15046,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>62,460.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -15197,15 +15056,10 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15224,12 +15078,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>349,231.0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -15238,11 +15092,6 @@
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15261,12 +15110,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>286,032.0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -15275,11 +15124,6 @@
         </is>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15298,12 +15142,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>394,504.0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -15312,11 +15156,6 @@
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15335,12 +15174,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>149,373.0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -15349,11 +15188,6 @@
         </is>
       </c>
       <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15372,12 +15206,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>89,739.0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -15386,11 +15220,6 @@
         </is>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15409,12 +15238,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>413,098.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -15423,11 +15252,6 @@
         </is>
       </c>
       <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15446,12 +15270,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>88,826.0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -15460,11 +15284,6 @@
         </is>
       </c>
       <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15483,12 +15302,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>76,947.24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15497,11 +15316,6 @@
         </is>
       </c>
       <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15520,12 +15334,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>76,035.0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -15534,11 +15348,6 @@
         </is>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15557,12 +15366,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>84,933.0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -15571,11 +15380,6 @@
         </is>
       </c>
       <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15594,12 +15398,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>26,151.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -15608,11 +15412,6 @@
         </is>
       </c>
       <c r="F34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15631,12 +15430,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>56,490.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -15645,11 +15444,6 @@
         </is>
       </c>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15668,12 +15462,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15,817.8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -15682,11 +15476,6 @@
         </is>
       </c>
       <c r="F36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15705,7 +15494,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3,544.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15715,15 +15504,10 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15742,12 +15526,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>32,997.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -15756,11 +15540,6 @@
         </is>
       </c>
       <c r="F38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15779,12 +15558,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7,388.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -15793,11 +15572,6 @@
         </is>
       </c>
       <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15816,12 +15590,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7,898.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -15830,11 +15604,6 @@
         </is>
       </c>
       <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15853,12 +15622,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>8,199.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -15867,11 +15636,6 @@
         </is>
       </c>
       <c r="F41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15890,7 +15654,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4,499.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -15904,11 +15668,6 @@
         </is>
       </c>
       <c r="F42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -15927,12 +15686,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5,899.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -15941,11 +15700,6 @@
         </is>
       </c>
       <c r="F43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -15964,12 +15718,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -15978,11 +15732,6 @@
         </is>
       </c>
       <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -16001,12 +15750,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -16015,11 +15764,6 @@
         </is>
       </c>
       <c r="F45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -16038,12 +15782,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1,499.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -16052,11 +15796,6 @@
         </is>
       </c>
       <c r="F46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -16073,11 +15812,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -16092,20 +15828,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>金额(元)</t>
+          <t>合规</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>合规</t>
+          <t>不合规</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>不合规</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
         <is>
           <t>门店合规率</t>
         </is>
@@ -16124,20 +15855,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>841,203.11</t>
+          <t>202</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
         <is>
           <t>93.95%</t>
         </is>
@@ -16156,20 +15882,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2,162,378.7</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>98.09%</t>
         </is>
@@ -16188,20 +15909,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>232,873.0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>87.01%</t>
         </is>
@@ -16220,20 +15936,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2,189,350.78</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>97.89%</t>
         </is>
@@ -16252,20 +15963,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>696,009.82</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>95.03%</t>
         </is>
@@ -16284,20 +15990,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>685,623.52</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>96.81%</t>
         </is>
@@ -16316,20 +16017,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>561,093.13</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>95.68%</t>
         </is>
@@ -16348,20 +16044,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>220,446.45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>87.5%</t>
         </is>
@@ -16380,20 +16071,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>228,456.62</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
         <is>
           <t>89.29%</t>
         </is>
@@ -16412,20 +16098,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>606,028.6</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>95.68%</t>
         </is>
@@ -16444,20 +16125,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>670,420.88</t>
+          <t>142</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>95.95%</t>
         </is>
@@ -16476,20 +16152,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>705,153.13</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>97.33%</t>
         </is>
@@ -16508,20 +16179,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1,515,683.0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>98.34%</t>
         </is>
@@ -16540,20 +16206,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>794,614.73</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>97.63%</t>
         </is>
@@ -16572,20 +16233,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>636,189.97</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>96.97%</t>
         </is>
@@ -16604,20 +16260,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1,176,119.98</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
         <is>
           <t>98.76%</t>
         </is>
@@ -16636,20 +16287,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1,138,315.36</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
         <is>
           <t>98.35%</t>
         </is>
@@ -16668,20 +16314,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>143,150.6</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>92.45%</t>
         </is>
@@ -16700,20 +16341,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>725,707.76</t>
+          <t>170</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>97.7%</t>
         </is>
@@ -16732,20 +16368,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>45,752.0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
         <is>
           <t>78.95%</t>
         </is>
@@ -16764,20 +16395,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>529,744.0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>97.39%</t>
         </is>
@@ -16796,20 +16422,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>53,907.0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>73.33%</t>
         </is>
@@ -16828,20 +16449,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>162,276.0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
         <is>
           <t>90.62%</t>
         </is>
@@ -16860,20 +16476,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>184,343.0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>95.59%</t>
         </is>
@@ -16892,20 +16503,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>362,431.0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
         <is>
           <t>97.37%</t>
         </is>
@@ -16924,20 +16530,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1,063,039.75</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>98.64%</t>
         </is>
@@ -16956,20 +16557,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>568,982.3</t>
+          <t>173</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
         <is>
           <t>98.3%</t>
         </is>
@@ -16988,20 +16584,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>580,575.1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
         <is>
           <t>94.83%</t>
         </is>
@@ -17020,20 +16611,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>333,188.0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
         <is>
           <t>96.59%</t>
         </is>
@@ -17052,20 +16638,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>692,491.42</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
         <is>
           <t>98.51%</t>
         </is>
@@ -17084,20 +16665,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>158,488.0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
         <is>
           <t>92.68%</t>
         </is>
@@ -17116,20 +16692,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>223,841.0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
         <is>
           <t>95.77%</t>
         </is>
@@ -17148,20 +16719,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>135,316.79</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
         <is>
           <t>91.43%</t>
         </is>
@@ -17180,20 +16746,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>101,737.87</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
         <is>
           <t>92.31%</t>
         </is>
@@ -17212,20 +16773,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>400,645.25</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
         <is>
           <t>97.14%</t>
         </is>
@@ -17244,20 +16800,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>202,531.0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
         <is>
           <t>96.72%</t>
         </is>
@@ -17276,20 +16827,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>613,319.6</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
         <is>
           <t>98.69%</t>
         </is>
@@ -17308,20 +16854,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>657,412.97</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
         <is>
           <t>98.15%</t>
         </is>
@@ -17340,20 +16881,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>732,384.95</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
         <is>
           <t>98.88%</t>
         </is>
@@ -17372,20 +16908,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>613,863.48</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
         <is>
           <t>98.8%</t>
         </is>
@@ -17404,20 +16935,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>715,704.6</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
         <is>
           <t>98.52%</t>
         </is>
@@ -17436,20 +16962,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>442,577.1</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
         <is>
           <t>98.47%</t>
         </is>
@@ -17468,20 +16989,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>159,525.0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
         <is>
           <t>96.08%</t>
         </is>
@@ -17500,20 +17016,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>626,610.03</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
         <is>
           <t>98.46%</t>
         </is>
@@ -17532,20 +17043,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1,001,526.42</t>
+          <t>195</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
         <is>
           <t>98.98%</t>
         </is>
@@ -17564,20 +17070,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>205,027.4</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
         <is>
           <t>97.06%</t>
         </is>
@@ -17596,20 +17097,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>185,832.0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
         <is>
           <t>96.08%</t>
         </is>
@@ -17628,20 +17124,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>611,646.86</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
         <is>
           <t>98.68%</t>
         </is>
@@ -17660,20 +17151,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>923,244.65</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
         <is>
           <t>98.94%</t>
         </is>
@@ -17692,20 +17178,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>466,836.32</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
         <is>
           <t>98.31%</t>
         </is>
@@ -17724,20 +17205,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>443,161.06</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
         <is>
           <t>98.96%</t>
         </is>
@@ -17756,20 +17232,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>468,973.0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
         <is>
           <t>99.34%</t>
         </is>
@@ -17788,20 +17259,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>253,227.0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
         <is>
           <t>98.75%</t>
         </is>
@@ -17820,20 +17286,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>483,920.59</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
         <is>
           <t>99.2%</t>
         </is>
@@ -17852,20 +17313,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>289,108.0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
         <is>
           <t>99.1%</t>
         </is>
@@ -17884,20 +17340,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>204,641.0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
         <is>
           <t>98.61%</t>
         </is>
@@ -17916,20 +17367,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>673,599.36</t>
+          <t>201</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
         <is>
           <t>99.5%</t>
         </is>
@@ -17948,20 +17394,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>132,613.2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
         <is>
           <t>98.15%</t>
         </is>
@@ -17980,20 +17421,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>147,433.0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
         <is>
           <t>97.92%</t>
         </is>
@@ -18012,20 +17448,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>181,386.52</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
         <is>
           <t>98.53%</t>
         </is>
@@ -18044,20 +17475,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>353,258.11</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
         <is>
           <t>98.84%</t>
         </is>
@@ -18076,20 +17502,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>780,384.16</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
         <is>
           <t>99.43%</t>
         </is>
@@ -18108,20 +17529,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>473,446.0</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
         <is>
           <t>99.33%</t>
         </is>
@@ -18140,20 +17556,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>979,027.15</t>
+          <t>237</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
         <is>
           <t>99.58%</t>
         </is>
@@ -18172,20 +17583,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>204,749.02</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
         <is>
           <t>97.73%</t>
         </is>
@@ -18204,20 +17610,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>331,844.0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
         <is>
           <t>99.05%</t>
         </is>
@@ -18236,20 +17637,15 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>351,181.7</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
         <is>
           <t>97.96%</t>
         </is>
@@ -18268,20 +17664,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>611,405.3</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
         <is>
           <t>99.29%</t>
         </is>
@@ -18300,20 +17691,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>226,189.0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
         <is>
           <t>98.39%</t>
         </is>
@@ -18332,20 +17718,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>724,293.34</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
         <is>
           <t>99.31%</t>
         </is>
@@ -18364,20 +17745,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>77,670.0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
         <is>
           <t>95.45%</t>
         </is>
@@ -18396,20 +17772,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>504,867.68</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
         <is>
           <t>99.14%</t>
         </is>
@@ -18428,20 +17799,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>347,808.68</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
         <is>
           <t>99.07%</t>
         </is>
@@ -18460,20 +17826,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>691,485.33</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
         <is>
           <t>99.4%</t>
         </is>
@@ -18492,20 +17853,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>186,939.0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
         <is>
           <t>96.3%</t>
         </is>
@@ -18524,20 +17880,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>700,800.42</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
         <is>
           <t>99.47%</t>
         </is>
@@ -18556,20 +17907,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>358,357.0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
         <is>
           <t>97.22%</t>
         </is>
@@ -18588,20 +17934,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>195,534.0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
         <is>
           <t>98.25%</t>
         </is>
@@ -18620,20 +17961,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>239,784.11</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
         <is>
           <t>98.84%</t>
         </is>
@@ -18652,20 +17988,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1,235,317.12</t>
+          <t>270</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
         <is>
           <t>99.63%</t>
         </is>
@@ -18684,20 +18015,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>168,777.2</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
         <is>
           <t>97.5%</t>
         </is>
@@ -18716,20 +18042,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>125,186.0</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
         <is>
           <t>97.73%</t>
         </is>
@@ -18748,20 +18069,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>206,310.65</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
         <is>
           <t>97.5%</t>
         </is>
@@ -18780,20 +18096,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>330,881.1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
         <is>
           <t>96.88%</t>
         </is>
@@ -18812,20 +18123,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>490,914.63</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
         <is>
           <t>99.03%</t>
         </is>
@@ -18844,20 +18150,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>259,516.25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
         <is>
           <t>98.59%</t>
         </is>
@@ -18876,20 +18177,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>484,450.2</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -18908,20 +18204,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>495,908.9</t>
+          <t>121</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -18940,20 +18231,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>452,489.05</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -18972,20 +18258,15 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>564,239.82</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19004,20 +18285,15 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>450,351.05</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19036,20 +18312,15 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1,708,559.8</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19068,20 +18339,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1,043,898.1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19100,20 +18366,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>213,610.0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19132,20 +18393,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1,048,804.48</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19164,20 +18420,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>179,930.2</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19196,20 +18447,15 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>538,286.05</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19228,20 +18474,15 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>377,434.45</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19260,20 +18501,15 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1,067,328.67</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19292,20 +18528,15 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>660,460.34</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19324,20 +18555,15 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>786,784.72</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19356,20 +18582,15 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>970,692.31</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19388,20 +18609,15 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>116,565.0</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19420,20 +18636,15 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>145,871.55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19452,20 +18663,15 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>264,586.0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19484,20 +18690,15 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>507,951.9</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19516,20 +18717,15 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>422,377.17</t>
+          <t>145</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19548,20 +18744,15 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>347,651.65</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19580,20 +18771,15 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>212,154.0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19612,20 +18798,15 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>428,957.08</t>
+          <t>126</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19644,20 +18825,15 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>683,954.88</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19676,20 +18852,15 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>259,464.48</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19708,20 +18879,15 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>297,040.0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19740,20 +18906,15 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>782,634.29</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19772,20 +18933,15 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>251,133.0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19804,20 +18960,15 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>580,160.0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19836,20 +18987,15 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>228,802.8</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19868,20 +19014,15 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>575,354.8</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19900,20 +19041,15 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1,364,077.71</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19932,20 +19068,15 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>319,278.86</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19964,20 +19095,15 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>316,487.15</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -19996,20 +19122,15 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>214,516.0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20028,20 +19149,15 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>214,059.21</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20060,20 +19176,15 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>81,860.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20092,20 +19203,15 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>801,911.23</t>
+          <t>121</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20124,20 +19230,15 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>142,203.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20156,20 +19257,15 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>660,116.6</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20188,20 +19284,15 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>169,675.0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20220,20 +19311,15 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>139,502.0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20252,20 +19338,15 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>751,871.2</t>
+          <t>176</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20284,20 +19365,15 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1,062,099.13</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20316,20 +19392,15 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>593,617.72</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20348,20 +19419,15 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>199,941.0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20380,20 +19446,15 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>150,278.0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20412,20 +19473,15 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1,533,469.0</t>
+          <t>361</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20444,20 +19500,15 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>997,623.54</t>
+          <t>239</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20476,20 +19527,15 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>292,472.74</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20508,20 +19554,15 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>180,168.0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20540,20 +19581,15 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>126,728.0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20572,20 +19608,15 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>146,891.0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20604,20 +19635,15 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>729,343.03</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20636,20 +19662,15 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>327,409.44</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20668,20 +19689,15 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>243,694.0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20700,20 +19716,15 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>210,278.0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20732,20 +19743,15 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>541,268.25</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20764,20 +19770,15 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>421,065.0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20796,20 +19797,15 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>432,407.63</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20828,20 +19824,15 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>344,719.0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20860,20 +19851,15 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>81,568.0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20892,20 +19878,15 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>386,757.48</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20924,20 +19905,15 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>579,700.02</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20956,20 +19932,15 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>894,243.08</t>
+          <t>201</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -20988,20 +19959,15 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>437,615.18</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21020,20 +19986,15 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>67,909.0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21052,20 +20013,15 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>530,604.38</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21084,20 +20040,15 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>87,785.0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21116,20 +20067,15 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>320,198.91</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21148,20 +20094,15 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>514,466.47</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21180,20 +20121,15 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>51,208.1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21212,20 +20148,15 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>276,550.0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21244,20 +20175,15 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>130,687.0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21276,20 +20202,15 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>313,049.94</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21308,20 +20229,15 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>211,768.0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21340,20 +20256,15 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>74,717.08</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21372,20 +20283,15 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>395,983.61</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21404,20 +20310,15 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>141,209.77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21436,20 +20337,15 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>202,232.0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21468,20 +20364,15 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>270,286.52</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21500,20 +20391,15 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>14,689.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21532,20 +20418,15 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>122,309.0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21564,20 +20445,15 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>40,869.81</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21596,20 +20472,15 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>39,994.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -21626,11 +20497,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -21660,20 +20528,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>金额(元)</t>
+          <t>合规</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>合规</t>
+          <t>不合规</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>不合规</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>分公司合规率</t>
         </is>
@@ -21707,20 +20570,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24,971,246.54</t>
+          <t>6,010</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6,010</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>98.56%</t>
         </is>
@@ -21754,20 +20612,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24,854,211.39</t>
+          <t>5,351</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5,351</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>98.49%</t>
         </is>
@@ -21801,20 +20654,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9,357,404.74</t>
+          <t>2,702</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,702</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>98.76%</t>
         </is>
@@ -21848,20 +20696,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,245,256.34</t>
+          <t>1,004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,004</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>97.67%</t>
         </is>
@@ -21895,20 +20738,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11,866,078.22</t>
+          <t>2,808</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2,808</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>99.72%</t>
         </is>
@@ -21942,20 +20780,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6,866,731.08</t>
+          <t>1,783</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1,783</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>99.83%</t>
         </is>
